--- a/材料科学基础_双一流招生数据_2025.xlsx
+++ b/材料科学基础_双一流招生数据_2025.xlsx
@@ -11,7 +11,7 @@
     <sheet name="使用指南" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'材料科学基础招生数据'!$A$2:$P$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'材料科学基础招生数据'!$A$2:$P$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P86"/>
+  <dimension ref="A1:P201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6894,8 +6894,8618 @@
         </is>
       </c>
     </row>
+    <row r="87" ht="16" customHeight="1">
+      <c r="A87" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>080501</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>材料物理与化学</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H87" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J87" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K87" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L87" s="6" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="M87" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N87" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O87" s="6" t="inlineStr">
+        <is>
+          <t>化学/材料科学</t>
+        </is>
+      </c>
+      <c r="P87" s="6" t="inlineStr"/>
+    </row>
+    <row r="88" ht="16" customHeight="1">
+      <c r="A88" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L88" s="4" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="M88" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N88" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O88" s="4" t="inlineStr">
+        <is>
+          <t>化学/材料科学</t>
+        </is>
+      </c>
+      <c r="P88" s="4" t="inlineStr"/>
+    </row>
+    <row r="89" ht="16" customHeight="1">
+      <c r="A89" s="8" t="n">
+        <v>86</v>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>南开大学</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H89" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="I89" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J89" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K89" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L89" s="8" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="M89" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N89" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O89" s="8" t="inlineStr">
+        <is>
+          <t>化学/材料科学</t>
+        </is>
+      </c>
+      <c r="P89" s="8" t="inlineStr"/>
+    </row>
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>燕山大学</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>080501</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>材料物理与化学</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L90" s="4" t="inlineStr">
+        <is>
+          <t>837</t>
+        </is>
+      </c>
+      <c r="M90" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N90" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O90" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程/机械工程</t>
+        </is>
+      </c>
+      <c r="P90" s="4" t="inlineStr">
+        <is>
+          <t>亚稳材料国家重点实验室</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="16" customHeight="1">
+      <c r="A91" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>燕山大学</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J91" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K91" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L91" s="6" t="inlineStr">
+        <is>
+          <t>837</t>
+        </is>
+      </c>
+      <c r="M91" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N91" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O91" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程/机械工程</t>
+        </is>
+      </c>
+      <c r="P91" s="6" t="inlineStr"/>
+    </row>
+    <row r="92" ht="16" customHeight="1">
+      <c r="A92" s="4" t="n">
+        <v>89</v>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>燕山大学</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>080503</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>材料加工工程</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L92" s="4" t="inlineStr">
+        <is>
+          <t>837</t>
+        </is>
+      </c>
+      <c r="M92" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N92" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O92" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程/机械工程</t>
+        </is>
+      </c>
+      <c r="P92" s="4" t="inlineStr"/>
+    </row>
+    <row r="93" ht="16" customHeight="1">
+      <c r="A93" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>燕山大学</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H93" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="I93" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J93" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K93" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L93" s="8" t="inlineStr">
+        <is>
+          <t>837</t>
+        </is>
+      </c>
+      <c r="M93" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N93" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O93" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程/机械工程</t>
+        </is>
+      </c>
+      <c r="P93" s="8" t="inlineStr"/>
+    </row>
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>太原理工大学</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>山西</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L94" s="4" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="M94" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N94" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O94" s="4" t="inlineStr">
+        <is>
+          <t>化学工程与技术/材料科学</t>
+        </is>
+      </c>
+      <c r="P94" s="4" t="inlineStr"/>
+    </row>
+    <row r="95" ht="16" customHeight="1">
+      <c r="A95" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>太原理工大学</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>山西</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>080503</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>材料加工工程</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H95" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J95" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K95" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L95" s="6" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="M95" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N95" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O95" s="6" t="inlineStr">
+        <is>
+          <t>化学工程与技术/材料科学</t>
+        </is>
+      </c>
+      <c r="P95" s="6" t="inlineStr"/>
+    </row>
+    <row r="96" ht="16" customHeight="1">
+      <c r="A96" s="8" t="n">
+        <v>93</v>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>太原理工大学</t>
+        </is>
+      </c>
+      <c r="C96" s="8" t="inlineStr">
+        <is>
+          <t>山西</t>
+        </is>
+      </c>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F96" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G96" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H96" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="I96" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J96" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K96" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L96" s="8" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="M96" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N96" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O96" s="8" t="inlineStr">
+        <is>
+          <t>化学工程与技术/材料科学</t>
+        </is>
+      </c>
+      <c r="P96" s="8" t="inlineStr"/>
+    </row>
+    <row r="97" ht="16" customHeight="1">
+      <c r="A97" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>内蒙古大学</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>内蒙古</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H97" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J97" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K97" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L97" s="6" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M97" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N97" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O97" s="6" t="inlineStr">
+        <is>
+          <t>化学</t>
+        </is>
+      </c>
+      <c r="P97" s="6" t="inlineStr"/>
+    </row>
+    <row r="98" ht="16" customHeight="1">
+      <c r="A98" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>哈尔滨工程大学</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>黑龙江</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与化学工程学院</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>080501</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>材料物理与化学</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J98" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L98" s="4" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M98" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N98" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O98" s="4" t="inlineStr">
+        <is>
+          <t>船舶与海洋工程/材料</t>
+        </is>
+      </c>
+      <c r="P98" s="4" t="inlineStr"/>
+    </row>
+    <row r="99" ht="16" customHeight="1">
+      <c r="A99" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>哈尔滨工程大学</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>黑龙江</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与化学工程学院</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H99" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J99" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K99" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L99" s="6" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M99" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N99" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O99" s="6" t="inlineStr">
+        <is>
+          <t>船舶与海洋工程/材料</t>
+        </is>
+      </c>
+      <c r="P99" s="6" t="inlineStr"/>
+    </row>
+    <row r="100" ht="16" customHeight="1">
+      <c r="A100" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>哈尔滨工程大学</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t>黑龙江</t>
+        </is>
+      </c>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与化学工程学院</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F100" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G100" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H100" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="I100" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J100" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K100" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L100" s="8" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M100" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N100" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O100" s="8" t="inlineStr">
+        <is>
+          <t>船舶与海洋工程/材料</t>
+        </is>
+      </c>
+      <c r="P100" s="8" t="inlineStr"/>
+    </row>
+    <row r="101" ht="16" customHeight="1">
+      <c r="A101" s="6" t="n">
+        <v>98</v>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>材料科学系</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>080501</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>材料物理与化学</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J101" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K101" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L101" s="6" t="inlineStr">
+        <is>
+          <t>自命题</t>
+        </is>
+      </c>
+      <c r="M101" s="10" t="inlineStr">
+        <is>
+          <t>材料科学基础*</t>
+        </is>
+      </c>
+      <c r="N101" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O101" s="6" t="inlineStr">
+        <is>
+          <t>化学/材料科学</t>
+        </is>
+      </c>
+      <c r="P101" s="10" t="inlineStr">
+        <is>
+          <t>★以招生简章为准</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="16" customHeight="1">
+      <c r="A102" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>材料科学系</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J102" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L102" s="4" t="inlineStr">
+        <is>
+          <t>自命题</t>
+        </is>
+      </c>
+      <c r="M102" s="11" t="inlineStr">
+        <is>
+          <t>材料科学基础*</t>
+        </is>
+      </c>
+      <c r="N102" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O102" s="4" t="inlineStr">
+        <is>
+          <t>化学/材料科学</t>
+        </is>
+      </c>
+      <c r="P102" s="11" t="inlineStr">
+        <is>
+          <t>★以招生简章为准</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="16" customHeight="1">
+      <c r="A103" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>华东理工大学</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>080501</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>材料物理与化学</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H103" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J103" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K103" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L103" s="6" t="inlineStr">
+        <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="M103" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N103" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O103" s="6" t="inlineStr">
+        <is>
+          <t>化学工程与技术/材料</t>
+        </is>
+      </c>
+      <c r="P103" s="6" t="inlineStr"/>
+    </row>
+    <row r="104" ht="16" customHeight="1">
+      <c r="A104" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>华东理工大学</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J104" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L104" s="4" t="inlineStr">
+        <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="M104" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N104" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O104" s="4" t="inlineStr">
+        <is>
+          <t>化学工程与技术/材料</t>
+        </is>
+      </c>
+      <c r="P104" s="4" t="inlineStr"/>
+    </row>
+    <row r="105" ht="16" customHeight="1">
+      <c r="A105" s="6" t="n">
+        <v>102</v>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>华东理工大学</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>080503</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>材料加工工程</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H105" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J105" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K105" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L105" s="6" t="inlineStr">
+        <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="M105" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N105" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O105" s="6" t="inlineStr">
+        <is>
+          <t>化学工程与技术/材料</t>
+        </is>
+      </c>
+      <c r="P105" s="6" t="inlineStr"/>
+    </row>
+    <row r="106" ht="16" customHeight="1">
+      <c r="A106" s="8" t="n">
+        <v>103</v>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>华东理工大学</t>
+        </is>
+      </c>
+      <c r="C106" s="8" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="D106" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F106" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G106" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H106" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="I106" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K106" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L106" s="8" t="inlineStr">
+        <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="M106" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N106" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O106" s="8" t="inlineStr">
+        <is>
+          <t>化学工程与技术/材料</t>
+        </is>
+      </c>
+      <c r="P106" s="8" t="inlineStr"/>
+    </row>
+    <row r="107" ht="16" customHeight="1">
+      <c r="A107" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>东华大学</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>080501</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>材料物理与化学</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H107" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J107" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K107" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L107" s="6" t="inlineStr">
+        <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="M107" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N107" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O107" s="6" t="inlineStr">
+        <is>
+          <t>纺织科学与工程/材料</t>
+        </is>
+      </c>
+      <c r="P107" s="6" t="inlineStr">
+        <is>
+          <t>纤维材料及功能材料方向</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="16" customHeight="1">
+      <c r="A108" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>东华大学</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J108" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L108" s="4" t="inlineStr">
+        <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="M108" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N108" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O108" s="4" t="inlineStr">
+        <is>
+          <t>纺织科学与工程/材料</t>
+        </is>
+      </c>
+      <c r="P108" s="4" t="inlineStr"/>
+    </row>
+    <row r="109" ht="16" customHeight="1">
+      <c r="A109" s="8" t="n">
+        <v>106</v>
+      </c>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
+          <t>东华大学</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F109" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G109" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H109" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="I109" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J109" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K109" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L109" s="8" t="inlineStr">
+        <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="M109" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N109" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O109" s="8" t="inlineStr">
+        <is>
+          <t>纺织科学与工程/材料</t>
+        </is>
+      </c>
+      <c r="P109" s="8" t="inlineStr"/>
+    </row>
+    <row r="110" ht="16" customHeight="1">
+      <c r="A110" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>上海大学</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>080501</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>材料物理与化学</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J110" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L110" s="4" t="inlineStr">
+        <is>
+          <t>833</t>
+        </is>
+      </c>
+      <c r="M110" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N110" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O110" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程</t>
+        </is>
+      </c>
+      <c r="P110" s="4" t="inlineStr"/>
+    </row>
+    <row r="111" ht="16" customHeight="1">
+      <c r="A111" s="6" t="n">
+        <v>108</v>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>上海大学</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H111" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J111" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K111" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L111" s="6" t="inlineStr">
+        <is>
+          <t>833</t>
+        </is>
+      </c>
+      <c r="M111" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N111" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O111" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程</t>
+        </is>
+      </c>
+      <c r="P111" s="6" t="inlineStr"/>
+    </row>
+    <row r="112" ht="16" customHeight="1">
+      <c r="A112" s="8" t="n">
+        <v>109</v>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>上海大学</t>
+        </is>
+      </c>
+      <c r="C112" s="8" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="D112" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E112" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F112" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G112" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H112" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="I112" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J112" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K112" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L112" s="8" t="inlineStr">
+        <is>
+          <t>833</t>
+        </is>
+      </c>
+      <c r="M112" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N112" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O112" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程</t>
+        </is>
+      </c>
+      <c r="P112" s="8" t="inlineStr"/>
+    </row>
+    <row r="113" ht="16" customHeight="1">
+      <c r="A113" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>南京理工大学</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>080501</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>材料物理与化学</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H113" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J113" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K113" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L113" s="6" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="M113" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N113" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O113" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程/兵器科学与技术</t>
+        </is>
+      </c>
+      <c r="P113" s="6" t="inlineStr"/>
+    </row>
+    <row r="114" ht="16" customHeight="1">
+      <c r="A114" s="4" t="n">
+        <v>111</v>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>南京理工大学</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J114" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L114" s="4" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="M114" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N114" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O114" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程/兵器科学与技术</t>
+        </is>
+      </c>
+      <c r="P114" s="4" t="inlineStr"/>
+    </row>
+    <row r="115" ht="16" customHeight="1">
+      <c r="A115" s="6" t="n">
+        <v>112</v>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>南京理工大学</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>080503</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>材料加工工程</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H115" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J115" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K115" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L115" s="6" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="M115" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N115" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O115" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程/兵器科学与技术</t>
+        </is>
+      </c>
+      <c r="P115" s="6" t="inlineStr"/>
+    </row>
+    <row r="116" ht="16" customHeight="1">
+      <c r="A116" s="8" t="n">
+        <v>113</v>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>南京理工大学</t>
+        </is>
+      </c>
+      <c r="C116" s="8" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="D116" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E116" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F116" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G116" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H116" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="I116" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J116" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K116" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L116" s="8" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="M116" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N116" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O116" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程/兵器科学与技术</t>
+        </is>
+      </c>
+      <c r="P116" s="8" t="inlineStr"/>
+    </row>
+    <row r="117" ht="16" customHeight="1">
+      <c r="A117" s="6" t="n">
+        <v>114</v>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>南京航空航天大学</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与技术学院</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G117" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H117" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J117" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K117" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L117" s="6" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="M117" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N117" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O117" s="6" t="inlineStr">
+        <is>
+          <t>航空宇航科学与技术/材料</t>
+        </is>
+      </c>
+      <c r="P117" s="6" t="inlineStr"/>
+    </row>
+    <row r="118" ht="16" customHeight="1">
+      <c r="A118" s="4" t="n">
+        <v>115</v>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>南京航空航天大学</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与技术学院</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>080503</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>材料加工工程</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I118" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L118" s="4" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="M118" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N118" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O118" s="4" t="inlineStr">
+        <is>
+          <t>航空宇航科学与技术/材料</t>
+        </is>
+      </c>
+      <c r="P118" s="4" t="inlineStr"/>
+    </row>
+    <row r="119" ht="16" customHeight="1">
+      <c r="A119" s="8" t="n">
+        <v>116</v>
+      </c>
+      <c r="B119" s="8" t="inlineStr">
+        <is>
+          <t>南京航空航天大学</t>
+        </is>
+      </c>
+      <c r="C119" s="8" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与技术学院</t>
+        </is>
+      </c>
+      <c r="E119" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F119" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G119" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H119" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="I119" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J119" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K119" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L119" s="8" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="M119" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N119" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O119" s="8" t="inlineStr">
+        <is>
+          <t>航空宇航科学与技术/材料</t>
+        </is>
+      </c>
+      <c r="P119" s="8" t="inlineStr"/>
+    </row>
+    <row r="120" ht="16" customHeight="1">
+      <c r="A120" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>中国矿业大学</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I120" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J120" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L120" s="4" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M120" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N120" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O120" s="4" t="inlineStr">
+        <is>
+          <t>矿业工程/安全科学与工程</t>
+        </is>
+      </c>
+      <c r="P120" s="4" t="inlineStr">
+        <is>
+          <t>徐州校区</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="16" customHeight="1">
+      <c r="A121" s="8" t="n">
+        <v>118</v>
+      </c>
+      <c r="B121" s="8" t="inlineStr">
+        <is>
+          <t>中国矿业大学</t>
+        </is>
+      </c>
+      <c r="C121" s="8" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="D121" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E121" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F121" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G121" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H121" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="I121" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J121" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K121" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L121" s="8" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M121" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N121" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O121" s="8" t="inlineStr">
+        <is>
+          <t>矿业工程/安全科学与工程</t>
+        </is>
+      </c>
+      <c r="P121" s="8" t="inlineStr">
+        <is>
+          <t>徐州校区</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="16" customHeight="1">
+      <c r="A122" s="4" t="n">
+        <v>119</v>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>苏州大学</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>材料与化学化工学部</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I122" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J122" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L122" s="4" t="inlineStr">
+        <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="M122" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N122" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O122" s="4" t="inlineStr">
+        <is>
+          <t>纺织科学与工程/材料</t>
+        </is>
+      </c>
+      <c r="P122" s="4" t="inlineStr"/>
+    </row>
+    <row r="123" ht="16" customHeight="1">
+      <c r="A123" s="8" t="n">
+        <v>120</v>
+      </c>
+      <c r="B123" s="8" t="inlineStr">
+        <is>
+          <t>苏州大学</t>
+        </is>
+      </c>
+      <c r="C123" s="8" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="D123" s="8" t="inlineStr">
+        <is>
+          <t>材料与化学化工学部</t>
+        </is>
+      </c>
+      <c r="E123" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F123" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G123" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H123" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="I123" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J123" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K123" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L123" s="8" t="inlineStr">
+        <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="M123" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N123" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O123" s="8" t="inlineStr">
+        <is>
+          <t>纺织科学与工程/材料</t>
+        </is>
+      </c>
+      <c r="P123" s="8" t="inlineStr"/>
+    </row>
+    <row r="124" ht="16" customHeight="1">
+      <c r="A124" s="4" t="n">
+        <v>121</v>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>江南大学</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I124" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J124" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L124" s="4" t="inlineStr">
+        <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="M124" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N124" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O124" s="4" t="inlineStr">
+        <is>
+          <t>食品科学与工程/材料</t>
+        </is>
+      </c>
+      <c r="P124" s="4" t="inlineStr"/>
+    </row>
+    <row r="125" ht="16" customHeight="1">
+      <c r="A125" s="8" t="n">
+        <v>122</v>
+      </c>
+      <c r="B125" s="8" t="inlineStr">
+        <is>
+          <t>江南大学</t>
+        </is>
+      </c>
+      <c r="C125" s="8" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="D125" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E125" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F125" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G125" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H125" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="I125" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J125" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K125" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L125" s="8" t="inlineStr">
+        <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="M125" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N125" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O125" s="8" t="inlineStr">
+        <is>
+          <t>食品科学与工程/材料</t>
+        </is>
+      </c>
+      <c r="P125" s="8" t="inlineStr"/>
+    </row>
+    <row r="126" ht="16" customHeight="1">
+      <c r="A126" s="4" t="n">
+        <v>123</v>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>南昌大学</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>江西</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>080501</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>材料物理与化学</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H126" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I126" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J126" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L126" s="4" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M126" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N126" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O126" s="4" t="inlineStr">
+        <is>
+          <t>食品科学/材料科学</t>
+        </is>
+      </c>
+      <c r="P126" s="4" t="inlineStr"/>
+    </row>
+    <row r="127" ht="16" customHeight="1">
+      <c r="A127" s="6" t="n">
+        <v>124</v>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>南昌大学</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>江西</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G127" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H127" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J127" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K127" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L127" s="6" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M127" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N127" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O127" s="6" t="inlineStr">
+        <is>
+          <t>食品科学/材料科学</t>
+        </is>
+      </c>
+      <c r="P127" s="6" t="inlineStr"/>
+    </row>
+    <row r="128" ht="16" customHeight="1">
+      <c r="A128" s="8" t="n">
+        <v>125</v>
+      </c>
+      <c r="B128" s="8" t="inlineStr">
+        <is>
+          <t>南昌大学</t>
+        </is>
+      </c>
+      <c r="C128" s="8" t="inlineStr">
+        <is>
+          <t>江西</t>
+        </is>
+      </c>
+      <c r="D128" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E128" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F128" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G128" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H128" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="I128" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J128" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K128" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L128" s="8" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M128" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N128" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O128" s="8" t="inlineStr">
+        <is>
+          <t>食品科学/材料科学</t>
+        </is>
+      </c>
+      <c r="P128" s="8" t="inlineStr"/>
+    </row>
+    <row r="129" ht="16" customHeight="1">
+      <c r="A129" s="6" t="n">
+        <v>126</v>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>中国海洋大学</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F129" s="6" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G129" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H129" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I129" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J129" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K129" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L129" s="6" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M129" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N129" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O129" s="6" t="inlineStr">
+        <is>
+          <t>海洋科学/水产学</t>
+        </is>
+      </c>
+      <c r="P129" s="6" t="inlineStr"/>
+    </row>
+    <row r="130" ht="16" customHeight="1">
+      <c r="A130" s="8" t="n">
+        <v>127</v>
+      </c>
+      <c r="B130" s="8" t="inlineStr">
+        <is>
+          <t>中国海洋大学</t>
+        </is>
+      </c>
+      <c r="C130" s="8" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="D130" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E130" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F130" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G130" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H130" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="I130" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J130" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K130" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L130" s="8" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M130" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N130" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O130" s="8" t="inlineStr">
+        <is>
+          <t>海洋科学/水产学</t>
+        </is>
+      </c>
+      <c r="P130" s="8" t="inlineStr"/>
+    </row>
+    <row r="131" ht="16" customHeight="1">
+      <c r="A131" s="6" t="n">
+        <v>128</v>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>中国石油大学（华东）</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F131" s="6" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G131" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H131" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J131" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K131" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L131" s="6" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M131" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N131" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O131" s="6" t="inlineStr">
+        <is>
+          <t>石油与天然气工程/化学工程</t>
+        </is>
+      </c>
+      <c r="P131" s="6" t="inlineStr">
+        <is>
+          <t>青岛校区</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="16" customHeight="1">
+      <c r="A132" s="8" t="n">
+        <v>129</v>
+      </c>
+      <c r="B132" s="8" t="inlineStr">
+        <is>
+          <t>中国石油大学（华东）</t>
+        </is>
+      </c>
+      <c r="C132" s="8" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="D132" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E132" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F132" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G132" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H132" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="I132" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J132" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K132" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L132" s="8" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M132" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N132" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O132" s="8" t="inlineStr">
+        <is>
+          <t>石油与天然气工程/化学工程</t>
+        </is>
+      </c>
+      <c r="P132" s="8" t="inlineStr"/>
+    </row>
+    <row r="133" ht="16" customHeight="1">
+      <c r="A133" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>郑州大学</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>080501</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>材料物理与化学</t>
+        </is>
+      </c>
+      <c r="G133" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H133" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J133" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K133" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L133" s="6" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M133" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N133" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O133" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程/化学</t>
+        </is>
+      </c>
+      <c r="P133" s="6" t="inlineStr"/>
+    </row>
+    <row r="134" ht="16" customHeight="1">
+      <c r="A134" s="4" t="n">
+        <v>131</v>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>郑州大学</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H134" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="I134" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J134" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L134" s="4" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M134" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N134" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O134" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程/化学</t>
+        </is>
+      </c>
+      <c r="P134" s="4" t="inlineStr"/>
+    </row>
+    <row r="135" ht="16" customHeight="1">
+      <c r="A135" s="8" t="n">
+        <v>132</v>
+      </c>
+      <c r="B135" s="8" t="inlineStr">
+        <is>
+          <t>郑州大学</t>
+        </is>
+      </c>
+      <c r="C135" s="8" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="D135" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E135" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F135" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G135" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H135" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="I135" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J135" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K135" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L135" s="8" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M135" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N135" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O135" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程/化学</t>
+        </is>
+      </c>
+      <c r="P135" s="8" t="inlineStr"/>
+    </row>
+    <row r="136" ht="16" customHeight="1">
+      <c r="A136" s="4" t="n">
+        <v>133</v>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>河南大学</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G136" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I136" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J136" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L136" s="4" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M136" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N136" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O136" s="4" t="inlineStr">
+        <is>
+          <t>物理学/化学</t>
+        </is>
+      </c>
+      <c r="P136" s="4" t="inlineStr"/>
+    </row>
+    <row r="137" ht="16" customHeight="1">
+      <c r="A137" s="8" t="n">
+        <v>134</v>
+      </c>
+      <c r="B137" s="8" t="inlineStr">
+        <is>
+          <t>河南大学</t>
+        </is>
+      </c>
+      <c r="C137" s="8" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="D137" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E137" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F137" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G137" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H137" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I137" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J137" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K137" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L137" s="8" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M137" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N137" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O137" s="8" t="inlineStr">
+        <is>
+          <t>物理学/化学</t>
+        </is>
+      </c>
+      <c r="P137" s="8" t="inlineStr"/>
+    </row>
+    <row r="138" ht="16" customHeight="1">
+      <c r="A138" s="4" t="n">
+        <v>135</v>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>武汉大学</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>材料与能源学部</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>080501</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>材料物理与化学</t>
+        </is>
+      </c>
+      <c r="G138" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H138" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I138" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J138" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L138" s="4" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M138" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N138" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O138" s="4" t="inlineStr">
+        <is>
+          <t>测绘科学与技术/化学</t>
+        </is>
+      </c>
+      <c r="P138" s="4" t="inlineStr"/>
+    </row>
+    <row r="139" ht="16" customHeight="1">
+      <c r="A139" s="6" t="n">
+        <v>136</v>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>武汉大学</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>材料与能源学部</t>
+        </is>
+      </c>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F139" s="6" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G139" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H139" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J139" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K139" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L139" s="6" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M139" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N139" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O139" s="6" t="inlineStr">
+        <is>
+          <t>测绘科学与技术/化学</t>
+        </is>
+      </c>
+      <c r="P139" s="6" t="inlineStr"/>
+    </row>
+    <row r="140" ht="16" customHeight="1">
+      <c r="A140" s="8" t="n">
+        <v>137</v>
+      </c>
+      <c r="B140" s="8" t="inlineStr">
+        <is>
+          <t>武汉大学</t>
+        </is>
+      </c>
+      <c r="C140" s="8" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="D140" s="8" t="inlineStr">
+        <is>
+          <t>材料与能源学部</t>
+        </is>
+      </c>
+      <c r="E140" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F140" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G140" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H140" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="I140" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J140" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K140" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L140" s="8" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M140" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N140" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O140" s="8" t="inlineStr">
+        <is>
+          <t>测绘科学与技术/化学</t>
+        </is>
+      </c>
+      <c r="P140" s="8" t="inlineStr"/>
+    </row>
+    <row r="141" ht="16" customHeight="1">
+      <c r="A141" s="6" t="n">
+        <v>138</v>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>武汉理工大学</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="inlineStr">
+        <is>
+          <t>080501</t>
+        </is>
+      </c>
+      <c r="F141" s="6" t="inlineStr">
+        <is>
+          <t>材料物理与化学</t>
+        </is>
+      </c>
+      <c r="G141" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H141" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J141" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K141" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L141" s="6" t="inlineStr">
+        <is>
+          <t>843</t>
+        </is>
+      </c>
+      <c r="M141" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N141" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O141" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程</t>
+        </is>
+      </c>
+      <c r="P141" s="6" t="inlineStr">
+        <is>
+          <t>国家材料科学重点高校</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="16" customHeight="1">
+      <c r="A142" s="4" t="n">
+        <v>139</v>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>武汉理工大学</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G142" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H142" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I142" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J142" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L142" s="4" t="inlineStr">
+        <is>
+          <t>843</t>
+        </is>
+      </c>
+      <c r="M142" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N142" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O142" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程</t>
+        </is>
+      </c>
+      <c r="P142" s="4" t="inlineStr"/>
+    </row>
+    <row r="143" ht="16" customHeight="1">
+      <c r="A143" s="6" t="n">
+        <v>140</v>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>武汉理工大学</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>080503</t>
+        </is>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
+        <is>
+          <t>材料加工工程</t>
+        </is>
+      </c>
+      <c r="G143" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H143" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J143" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K143" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L143" s="6" t="inlineStr">
+        <is>
+          <t>843</t>
+        </is>
+      </c>
+      <c r="M143" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N143" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O143" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程</t>
+        </is>
+      </c>
+      <c r="P143" s="6" t="inlineStr"/>
+    </row>
+    <row r="144" ht="16" customHeight="1">
+      <c r="A144" s="8" t="n">
+        <v>141</v>
+      </c>
+      <c r="B144" s="8" t="inlineStr">
+        <is>
+          <t>武汉理工大学</t>
+        </is>
+      </c>
+      <c r="C144" s="8" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="D144" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E144" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F144" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G144" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H144" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="I144" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K144" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L144" s="8" t="inlineStr">
+        <is>
+          <t>843</t>
+        </is>
+      </c>
+      <c r="M144" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N144" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O144" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程</t>
+        </is>
+      </c>
+      <c r="P144" s="8" t="inlineStr">
+        <is>
+          <t>全日制专硕招生规模大</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="16" customHeight="1">
+      <c r="A145" s="6" t="n">
+        <v>142</v>
+      </c>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>中国地质大学（武汉）</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="D145" s="6" t="inlineStr">
+        <is>
+          <t>材料与化学学院</t>
+        </is>
+      </c>
+      <c r="E145" s="6" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F145" s="6" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G145" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H145" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J145" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K145" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L145" s="6" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M145" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N145" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O145" s="6" t="inlineStr">
+        <is>
+          <t>地质学/地质资源与地质工程</t>
+        </is>
+      </c>
+      <c r="P145" s="6" t="inlineStr"/>
+    </row>
+    <row r="146" ht="16" customHeight="1">
+      <c r="A146" s="8" t="n">
+        <v>143</v>
+      </c>
+      <c r="B146" s="8" t="inlineStr">
+        <is>
+          <t>中国地质大学（武汉）</t>
+        </is>
+      </c>
+      <c r="C146" s="8" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="D146" s="8" t="inlineStr">
+        <is>
+          <t>材料与化学学院</t>
+        </is>
+      </c>
+      <c r="E146" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F146" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G146" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H146" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="I146" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J146" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K146" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L146" s="8" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M146" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N146" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O146" s="8" t="inlineStr">
+        <is>
+          <t>地质学/地质资源与地质工程</t>
+        </is>
+      </c>
+      <c r="P146" s="8" t="inlineStr"/>
+    </row>
+    <row r="147" ht="16" customHeight="1">
+      <c r="A147" s="6" t="n">
+        <v>144</v>
+      </c>
+      <c r="B147" s="6" t="inlineStr">
+        <is>
+          <t>湘潭大学</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E147" s="6" t="inlineStr">
+        <is>
+          <t>080501</t>
+        </is>
+      </c>
+      <c r="F147" s="6" t="inlineStr">
+        <is>
+          <t>材料物理与化学</t>
+        </is>
+      </c>
+      <c r="G147" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H147" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J147" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K147" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L147" s="6" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M147" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N147" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O147" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程/化学</t>
+        </is>
+      </c>
+      <c r="P147" s="6" t="inlineStr">
+        <is>
+          <t>材料学实力强</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="16" customHeight="1">
+      <c r="A148" s="4" t="n">
+        <v>145</v>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>湘潭大学</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G148" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H148" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="I148" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J148" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L148" s="4" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M148" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N148" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O148" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程/化学</t>
+        </is>
+      </c>
+      <c r="P148" s="4" t="inlineStr"/>
+    </row>
+    <row r="149" ht="16" customHeight="1">
+      <c r="A149" s="6" t="n">
+        <v>146</v>
+      </c>
+      <c r="B149" s="6" t="inlineStr">
+        <is>
+          <t>湘潭大学</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="D149" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E149" s="6" t="inlineStr">
+        <is>
+          <t>080503</t>
+        </is>
+      </c>
+      <c r="F149" s="6" t="inlineStr">
+        <is>
+          <t>材料加工工程</t>
+        </is>
+      </c>
+      <c r="G149" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H149" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I149" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J149" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K149" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L149" s="6" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M149" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N149" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O149" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程/化学</t>
+        </is>
+      </c>
+      <c r="P149" s="6" t="inlineStr"/>
+    </row>
+    <row r="150" ht="16" customHeight="1">
+      <c r="A150" s="8" t="n">
+        <v>147</v>
+      </c>
+      <c r="B150" s="8" t="inlineStr">
+        <is>
+          <t>湘潭大学</t>
+        </is>
+      </c>
+      <c r="C150" s="8" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="D150" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E150" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F150" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G150" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H150" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="I150" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J150" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K150" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L150" s="8" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M150" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N150" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O150" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程/化学</t>
+        </is>
+      </c>
+      <c r="P150" s="8" t="inlineStr"/>
+    </row>
+    <row r="151" ht="16" customHeight="1">
+      <c r="A151" s="6" t="n">
+        <v>148</v>
+      </c>
+      <c r="B151" s="6" t="inlineStr">
+        <is>
+          <t>国防科技大学</t>
+        </is>
+      </c>
+      <c r="C151" s="6" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="D151" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E151" s="6" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F151" s="6" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G151" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H151" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I151" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J151" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K151" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L151" s="6" t="inlineStr">
+        <is>
+          <t>自命题</t>
+        </is>
+      </c>
+      <c r="M151" s="10" t="inlineStr">
+        <is>
+          <t>材料科学基础*</t>
+        </is>
+      </c>
+      <c r="N151" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O151" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程/信息与通信工程</t>
+        </is>
+      </c>
+      <c r="P151" s="6" t="inlineStr">
+        <is>
+          <t>军校，招收应届非军人</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="16" customHeight="1">
+      <c r="A152" s="4" t="n">
+        <v>149</v>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>暨南大学</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="D152" s="4" t="inlineStr">
+        <is>
+          <t>理工学院/材料系</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G152" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H152" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I152" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J152" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L152" s="4" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M152" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N152" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O152" s="4" t="inlineStr">
+        <is>
+          <t>中国语言文学/材料</t>
+        </is>
+      </c>
+      <c r="P152" s="4" t="inlineStr"/>
+    </row>
+    <row r="153" ht="16" customHeight="1">
+      <c r="A153" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="B153" s="8" t="inlineStr">
+        <is>
+          <t>暨南大学</t>
+        </is>
+      </c>
+      <c r="C153" s="8" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="D153" s="8" t="inlineStr">
+        <is>
+          <t>理工学院/材料系</t>
+        </is>
+      </c>
+      <c r="E153" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F153" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G153" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H153" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I153" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J153" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K153" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L153" s="8" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M153" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N153" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O153" s="8" t="inlineStr">
+        <is>
+          <t>中国语言文学/材料</t>
+        </is>
+      </c>
+      <c r="P153" s="8" t="inlineStr"/>
+    </row>
+    <row r="154" ht="16" customHeight="1">
+      <c r="A154" s="4" t="n">
+        <v>151</v>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>华南师范大学</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="D154" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G154" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H154" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I154" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J154" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L154" s="4" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M154" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N154" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O154" s="4" t="inlineStr">
+        <is>
+          <t>光学工程/材料</t>
+        </is>
+      </c>
+      <c r="P154" s="4" t="inlineStr"/>
+    </row>
+    <row r="155" ht="16" customHeight="1">
+      <c r="A155" s="8" t="n">
+        <v>152</v>
+      </c>
+      <c r="B155" s="8" t="inlineStr">
+        <is>
+          <t>华南师范大学</t>
+        </is>
+      </c>
+      <c r="C155" s="8" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="D155" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E155" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F155" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G155" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H155" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="I155" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J155" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K155" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L155" s="8" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M155" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N155" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O155" s="8" t="inlineStr">
+        <is>
+          <t>光学工程/材料</t>
+        </is>
+      </c>
+      <c r="P155" s="8" t="inlineStr"/>
+    </row>
+    <row r="156" ht="16" customHeight="1">
+      <c r="A156" s="4" t="n">
+        <v>153</v>
+      </c>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>广西大学</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>广西</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G156" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H156" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I156" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J156" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L156" s="4" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M156" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N156" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O156" s="4" t="inlineStr">
+        <is>
+          <t>土木工程/亚热带农业生物资源</t>
+        </is>
+      </c>
+      <c r="P156" s="4" t="inlineStr"/>
+    </row>
+    <row r="157" ht="16" customHeight="1">
+      <c r="A157" s="8" t="n">
+        <v>154</v>
+      </c>
+      <c r="B157" s="8" t="inlineStr">
+        <is>
+          <t>广西大学</t>
+        </is>
+      </c>
+      <c r="C157" s="8" t="inlineStr">
+        <is>
+          <t>广西</t>
+        </is>
+      </c>
+      <c r="D157" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E157" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F157" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G157" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H157" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="I157" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J157" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K157" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L157" s="8" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M157" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N157" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O157" s="8" t="inlineStr">
+        <is>
+          <t>土木工程/亚热带农业生物资源</t>
+        </is>
+      </c>
+      <c r="P157" s="8" t="inlineStr"/>
+    </row>
+    <row r="158" ht="16" customHeight="1">
+      <c r="A158" s="4" t="n">
+        <v>155</v>
+      </c>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t>西南交通大学</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="D158" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G158" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H158" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I158" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J158" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K158" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L158" s="4" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M158" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N158" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O158" s="4" t="inlineStr">
+        <is>
+          <t>交通运输工程/土木工程</t>
+        </is>
+      </c>
+      <c r="P158" s="4" t="inlineStr"/>
+    </row>
+    <row r="159" ht="16" customHeight="1">
+      <c r="A159" s="6" t="n">
+        <v>156</v>
+      </c>
+      <c r="B159" s="6" t="inlineStr">
+        <is>
+          <t>西南交通大学</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="D159" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E159" s="6" t="inlineStr">
+        <is>
+          <t>080503</t>
+        </is>
+      </c>
+      <c r="F159" s="6" t="inlineStr">
+        <is>
+          <t>材料加工工程</t>
+        </is>
+      </c>
+      <c r="G159" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H159" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J159" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K159" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L159" s="6" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M159" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N159" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O159" s="6" t="inlineStr">
+        <is>
+          <t>交通运输工程/土木工程</t>
+        </is>
+      </c>
+      <c r="P159" s="6" t="inlineStr"/>
+    </row>
+    <row r="160" ht="16" customHeight="1">
+      <c r="A160" s="8" t="n">
+        <v>157</v>
+      </c>
+      <c r="B160" s="8" t="inlineStr">
+        <is>
+          <t>西南交通大学</t>
+        </is>
+      </c>
+      <c r="C160" s="8" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="D160" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E160" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F160" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G160" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H160" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="I160" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J160" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K160" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L160" s="8" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M160" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N160" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O160" s="8" t="inlineStr">
+        <is>
+          <t>交通运输工程/土木工程</t>
+        </is>
+      </c>
+      <c r="P160" s="8" t="inlineStr"/>
+    </row>
+    <row r="161" ht="16" customHeight="1">
+      <c r="A161" s="6" t="n">
+        <v>158</v>
+      </c>
+      <c r="B161" s="6" t="inlineStr">
+        <is>
+          <t>西南大学</t>
+        </is>
+      </c>
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="D161" s="6" t="inlineStr">
+        <is>
+          <t>材料与能源学院</t>
+        </is>
+      </c>
+      <c r="E161" s="6" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F161" s="6" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G161" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H161" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I161" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J161" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K161" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L161" s="6" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M161" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N161" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O161" s="6" t="inlineStr">
+        <is>
+          <t>作物学/园艺学</t>
+        </is>
+      </c>
+      <c r="P161" s="6" t="inlineStr"/>
+    </row>
+    <row r="162" ht="16" customHeight="1">
+      <c r="A162" s="8" t="n">
+        <v>159</v>
+      </c>
+      <c r="B162" s="8" t="inlineStr">
+        <is>
+          <t>西南大学</t>
+        </is>
+      </c>
+      <c r="C162" s="8" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="D162" s="8" t="inlineStr">
+        <is>
+          <t>材料与能源学院</t>
+        </is>
+      </c>
+      <c r="E162" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F162" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G162" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H162" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="I162" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J162" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K162" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L162" s="8" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M162" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N162" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O162" s="8" t="inlineStr">
+        <is>
+          <t>作物学/园艺学</t>
+        </is>
+      </c>
+      <c r="P162" s="8" t="inlineStr"/>
+    </row>
+    <row r="163" ht="16" customHeight="1">
+      <c r="A163" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="B163" s="6" t="inlineStr">
+        <is>
+          <t>贵州大学</t>
+        </is>
+      </c>
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t>材料与冶金学院</t>
+        </is>
+      </c>
+      <c r="E163" s="6" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F163" s="6" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G163" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H163" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I163" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J163" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K163" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L163" s="6" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M163" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N163" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O163" s="6" t="inlineStr">
+        <is>
+          <t>植物保护/材料科学</t>
+        </is>
+      </c>
+      <c r="P163" s="6" t="inlineStr"/>
+    </row>
+    <row r="164" ht="16" customHeight="1">
+      <c r="A164" s="4" t="n">
+        <v>161</v>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>贵州大学</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="D164" s="4" t="inlineStr">
+        <is>
+          <t>材料与冶金学院</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="inlineStr">
+        <is>
+          <t>080503</t>
+        </is>
+      </c>
+      <c r="F164" s="4" t="inlineStr">
+        <is>
+          <t>材料加工工程</t>
+        </is>
+      </c>
+      <c r="G164" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H164" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I164" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J164" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K164" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L164" s="4" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M164" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N164" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O164" s="4" t="inlineStr">
+        <is>
+          <t>植物保护/材料科学</t>
+        </is>
+      </c>
+      <c r="P164" s="4" t="inlineStr"/>
+    </row>
+    <row r="165" ht="16" customHeight="1">
+      <c r="A165" s="8" t="n">
+        <v>162</v>
+      </c>
+      <c r="B165" s="8" t="inlineStr">
+        <is>
+          <t>贵州大学</t>
+        </is>
+      </c>
+      <c r="C165" s="8" t="inlineStr">
+        <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="D165" s="8" t="inlineStr">
+        <is>
+          <t>材料与冶金学院</t>
+        </is>
+      </c>
+      <c r="E165" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F165" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G165" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H165" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I165" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J165" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K165" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L165" s="8" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M165" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N165" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O165" s="8" t="inlineStr">
+        <is>
+          <t>植物保护/材料科学</t>
+        </is>
+      </c>
+      <c r="P165" s="8" t="inlineStr"/>
+    </row>
+    <row r="166" ht="16" customHeight="1">
+      <c r="A166" s="4" t="n">
+        <v>163</v>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
+          <t>云南大学</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr">
+        <is>
+          <t>材料与能源学院</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G166" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H166" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I166" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J166" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K166" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L166" s="4" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M166" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N166" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O166" s="4" t="inlineStr">
+        <is>
+          <t>民族学/生态学</t>
+        </is>
+      </c>
+      <c r="P166" s="4" t="inlineStr"/>
+    </row>
+    <row r="167" ht="16" customHeight="1">
+      <c r="A167" s="8" t="n">
+        <v>164</v>
+      </c>
+      <c r="B167" s="8" t="inlineStr">
+        <is>
+          <t>云南大学</t>
+        </is>
+      </c>
+      <c r="C167" s="8" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="D167" s="8" t="inlineStr">
+        <is>
+          <t>材料与能源学院</t>
+        </is>
+      </c>
+      <c r="E167" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F167" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G167" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H167" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="I167" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J167" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K167" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L167" s="8" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M167" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N167" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O167" s="8" t="inlineStr">
+        <is>
+          <t>民族学/生态学</t>
+        </is>
+      </c>
+      <c r="P167" s="8" t="inlineStr"/>
+    </row>
+    <row r="168" ht="16" customHeight="1">
+      <c r="A168" s="4" t="n">
+        <v>165</v>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>西安电子科技大学</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="D168" s="4" t="inlineStr">
+        <is>
+          <t>先进材料与纳米科技学院</t>
+        </is>
+      </c>
+      <c r="E168" s="4" t="inlineStr">
+        <is>
+          <t>080501</t>
+        </is>
+      </c>
+      <c r="F168" s="4" t="inlineStr">
+        <is>
+          <t>材料物理与化学</t>
+        </is>
+      </c>
+      <c r="G168" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H168" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I168" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J168" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K168" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L168" s="4" t="inlineStr">
+        <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="M168" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N168" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O168" s="4" t="inlineStr">
+        <is>
+          <t>信息与通信工程/材料</t>
+        </is>
+      </c>
+      <c r="P168" s="4" t="inlineStr"/>
+    </row>
+    <row r="169" ht="16" customHeight="1">
+      <c r="A169" s="6" t="n">
+        <v>166</v>
+      </c>
+      <c r="B169" s="6" t="inlineStr">
+        <is>
+          <t>西安电子科技大学</t>
+        </is>
+      </c>
+      <c r="C169" s="6" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="D169" s="6" t="inlineStr">
+        <is>
+          <t>先进材料与纳米科技学院</t>
+        </is>
+      </c>
+      <c r="E169" s="6" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F169" s="6" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G169" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H169" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I169" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J169" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K169" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L169" s="6" t="inlineStr">
+        <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="M169" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N169" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O169" s="6" t="inlineStr">
+        <is>
+          <t>信息与通信工程/材料</t>
+        </is>
+      </c>
+      <c r="P169" s="6" t="inlineStr"/>
+    </row>
+    <row r="170" ht="16" customHeight="1">
+      <c r="A170" s="8" t="n">
+        <v>167</v>
+      </c>
+      <c r="B170" s="8" t="inlineStr">
+        <is>
+          <t>西安电子科技大学</t>
+        </is>
+      </c>
+      <c r="C170" s="8" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="D170" s="8" t="inlineStr">
+        <is>
+          <t>先进材料与纳米科技学院</t>
+        </is>
+      </c>
+      <c r="E170" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F170" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G170" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H170" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="I170" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J170" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K170" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L170" s="8" t="inlineStr">
+        <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="M170" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N170" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O170" s="8" t="inlineStr">
+        <is>
+          <t>信息与通信工程/材料</t>
+        </is>
+      </c>
+      <c r="P170" s="8" t="inlineStr"/>
+    </row>
+    <row r="171" ht="16" customHeight="1">
+      <c r="A171" s="6" t="n">
+        <v>168</v>
+      </c>
+      <c r="B171" s="6" t="inlineStr">
+        <is>
+          <t>西北大学</t>
+        </is>
+      </c>
+      <c r="C171" s="6" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="D171" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E171" s="6" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F171" s="6" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G171" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H171" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I171" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J171" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K171" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L171" s="6" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M171" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N171" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O171" s="6" t="inlineStr">
+        <is>
+          <t>地质学/化学</t>
+        </is>
+      </c>
+      <c r="P171" s="6" t="inlineStr"/>
+    </row>
+    <row r="172" ht="16" customHeight="1">
+      <c r="A172" s="8" t="n">
+        <v>169</v>
+      </c>
+      <c r="B172" s="8" t="inlineStr">
+        <is>
+          <t>西北大学</t>
+        </is>
+      </c>
+      <c r="C172" s="8" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="D172" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E172" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F172" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G172" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H172" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="I172" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J172" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K172" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L172" s="8" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M172" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N172" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O172" s="8" t="inlineStr">
+        <is>
+          <t>地质学/化学</t>
+        </is>
+      </c>
+      <c r="P172" s="8" t="inlineStr"/>
+    </row>
+    <row r="173" ht="16" customHeight="1">
+      <c r="A173" s="6" t="n">
+        <v>170</v>
+      </c>
+      <c r="B173" s="6" t="inlineStr">
+        <is>
+          <t>北京化工大学</t>
+        </is>
+      </c>
+      <c r="C173" s="6" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="D173" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E173" s="6" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F173" s="6" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G173" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H173" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="I173" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J173" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K173" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L173" s="6" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="M173" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N173" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O173" s="6" t="inlineStr">
+        <is>
+          <t>化学工程与技术/材料</t>
+        </is>
+      </c>
+      <c r="P173" s="6" t="inlineStr"/>
+    </row>
+    <row r="174" ht="16" customHeight="1">
+      <c r="A174" s="8" t="n">
+        <v>171</v>
+      </c>
+      <c r="B174" s="8" t="inlineStr">
+        <is>
+          <t>北京化工大学</t>
+        </is>
+      </c>
+      <c r="C174" s="8" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="D174" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E174" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F174" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G174" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H174" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="I174" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J174" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K174" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L174" s="8" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="M174" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N174" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O174" s="8" t="inlineStr">
+        <is>
+          <t>化学工程与技术/材料</t>
+        </is>
+      </c>
+      <c r="P174" s="8" t="inlineStr"/>
+    </row>
+    <row r="175" ht="16" customHeight="1">
+      <c r="A175" s="6" t="n">
+        <v>172</v>
+      </c>
+      <c r="B175" s="6" t="inlineStr">
+        <is>
+          <t>北京工业大学</t>
+        </is>
+      </c>
+      <c r="C175" s="6" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="D175" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E175" s="6" t="inlineStr">
+        <is>
+          <t>080501</t>
+        </is>
+      </c>
+      <c r="F175" s="6" t="inlineStr">
+        <is>
+          <t>材料物理与化学</t>
+        </is>
+      </c>
+      <c r="G175" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H175" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I175" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J175" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K175" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L175" s="6" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="M175" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N175" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O175" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程</t>
+        </is>
+      </c>
+      <c r="P175" s="6" t="inlineStr"/>
+    </row>
+    <row r="176" ht="16" customHeight="1">
+      <c r="A176" s="4" t="n">
+        <v>173</v>
+      </c>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t>北京工业大学</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="D176" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F176" s="4" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G176" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H176" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I176" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J176" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K176" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L176" s="4" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="M176" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N176" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O176" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程</t>
+        </is>
+      </c>
+      <c r="P176" s="4" t="inlineStr"/>
+    </row>
+    <row r="177" ht="16" customHeight="1">
+      <c r="A177" s="8" t="n">
+        <v>174</v>
+      </c>
+      <c r="B177" s="8" t="inlineStr">
+        <is>
+          <t>北京工业大学</t>
+        </is>
+      </c>
+      <c r="C177" s="8" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="D177" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E177" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F177" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G177" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H177" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="I177" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J177" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K177" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L177" s="8" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="M177" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N177" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O177" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程</t>
+        </is>
+      </c>
+      <c r="P177" s="8" t="inlineStr"/>
+    </row>
+    <row r="178" ht="16" customHeight="1">
+      <c r="A178" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
+          <t>华北电力大学</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="D178" s="4" t="inlineStr">
+        <is>
+          <t>新能源学院/材料系</t>
+        </is>
+      </c>
+      <c r="E178" s="4" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F178" s="4" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G178" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H178" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I178" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J178" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K178" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L178" s="4" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M178" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N178" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O178" s="4" t="inlineStr">
+        <is>
+          <t>电气工程/材料</t>
+        </is>
+      </c>
+      <c r="P178" s="4" t="inlineStr">
+        <is>
+          <t>北京/保定两校区</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="16" customHeight="1">
+      <c r="A179" s="8" t="n">
+        <v>176</v>
+      </c>
+      <c r="B179" s="8" t="inlineStr">
+        <is>
+          <t>华北电力大学</t>
+        </is>
+      </c>
+      <c r="C179" s="8" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="D179" s="8" t="inlineStr">
+        <is>
+          <t>新能源学院/材料系</t>
+        </is>
+      </c>
+      <c r="E179" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F179" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G179" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H179" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="I179" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J179" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K179" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L179" s="8" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M179" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N179" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O179" s="8" t="inlineStr">
+        <is>
+          <t>电气工程/材料</t>
+        </is>
+      </c>
+      <c r="P179" s="8" t="inlineStr"/>
+    </row>
+    <row r="180" ht="16" customHeight="1">
+      <c r="A180" s="4" t="n">
+        <v>177</v>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>中国石油大学（北京）</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="D180" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E180" s="4" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F180" s="4" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G180" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H180" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I180" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J180" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K180" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L180" s="4" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M180" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N180" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O180" s="4" t="inlineStr">
+        <is>
+          <t>石油与天然气工程</t>
+        </is>
+      </c>
+      <c r="P180" s="4" t="inlineStr"/>
+    </row>
+    <row r="181" ht="16" customHeight="1">
+      <c r="A181" s="8" t="n">
+        <v>178</v>
+      </c>
+      <c r="B181" s="8" t="inlineStr">
+        <is>
+          <t>中国石油大学（北京）</t>
+        </is>
+      </c>
+      <c r="C181" s="8" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="D181" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E181" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F181" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G181" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H181" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I181" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J181" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K181" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L181" s="8" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M181" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N181" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O181" s="8" t="inlineStr">
+        <is>
+          <t>石油与天然气工程</t>
+        </is>
+      </c>
+      <c r="P181" s="8" t="inlineStr"/>
+    </row>
+    <row r="182" ht="16" customHeight="1">
+      <c r="A182" s="4" t="n">
+        <v>179</v>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>中国地质大学（北京）</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E182" s="4" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F182" s="4" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G182" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H182" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I182" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J182" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K182" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L182" s="4" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M182" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N182" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O182" s="4" t="inlineStr">
+        <is>
+          <t>地质学/地质资源与地质工程</t>
+        </is>
+      </c>
+      <c r="P182" s="4" t="inlineStr"/>
+    </row>
+    <row r="183" ht="16" customHeight="1">
+      <c r="A183" s="8" t="n">
+        <v>180</v>
+      </c>
+      <c r="B183" s="8" t="inlineStr">
+        <is>
+          <t>中国地质大学（北京）</t>
+        </is>
+      </c>
+      <c r="C183" s="8" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="D183" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E183" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F183" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G183" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H183" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="I183" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J183" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K183" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L183" s="8" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M183" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N183" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O183" s="8" t="inlineStr">
+        <is>
+          <t>地质学/地质资源与地质工程</t>
+        </is>
+      </c>
+      <c r="P183" s="8" t="inlineStr"/>
+    </row>
+    <row r="184" ht="16" customHeight="1">
+      <c r="A184" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="B184" s="4" t="inlineStr">
+        <is>
+          <t>中国矿业大学（北京）</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="D184" s="4" t="inlineStr">
+        <is>
+          <t>化学与环境工程学院</t>
+        </is>
+      </c>
+      <c r="E184" s="4" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F184" s="4" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G184" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H184" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I184" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J184" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K184" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L184" s="4" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M184" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N184" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O184" s="4" t="inlineStr">
+        <is>
+          <t>矿业工程/安全科学与工程</t>
+        </is>
+      </c>
+      <c r="P184" s="4" t="inlineStr">
+        <is>
+          <t>北京校区，与徐州本部独立招生</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="16" customHeight="1">
+      <c r="A185" s="6" t="n">
+        <v>182</v>
+      </c>
+      <c r="B185" s="6" t="inlineStr">
+        <is>
+          <t>新疆大学</t>
+        </is>
+      </c>
+      <c r="C185" s="6" t="inlineStr">
+        <is>
+          <t>新疆</t>
+        </is>
+      </c>
+      <c r="D185" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与化学工程学院</t>
+        </is>
+      </c>
+      <c r="E185" s="6" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F185" s="6" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G185" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H185" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I185" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J185" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K185" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L185" s="6" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M185" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N185" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O185" s="6" t="inlineStr">
+        <is>
+          <t>计算机科学与技术/化学</t>
+        </is>
+      </c>
+      <c r="P185" s="6" t="inlineStr"/>
+    </row>
+    <row r="186" ht="16" customHeight="1">
+      <c r="A186" s="8" t="n">
+        <v>183</v>
+      </c>
+      <c r="B186" s="8" t="inlineStr">
+        <is>
+          <t>新疆大学</t>
+        </is>
+      </c>
+      <c r="C186" s="8" t="inlineStr">
+        <is>
+          <t>新疆</t>
+        </is>
+      </c>
+      <c r="D186" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与化学工程学院</t>
+        </is>
+      </c>
+      <c r="E186" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F186" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G186" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H186" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="I186" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J186" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K186" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L186" s="8" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M186" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N186" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O186" s="8" t="inlineStr">
+        <is>
+          <t>计算机科学与技术/化学</t>
+        </is>
+      </c>
+      <c r="P186" s="8" t="inlineStr"/>
+    </row>
+    <row r="187" ht="16" customHeight="1">
+      <c r="A187" s="6" t="n">
+        <v>184</v>
+      </c>
+      <c r="B187" s="6" t="inlineStr">
+        <is>
+          <t>福州大学</t>
+        </is>
+      </c>
+      <c r="C187" s="6" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="D187" s="6" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E187" s="6" t="inlineStr">
+        <is>
+          <t>080501</t>
+        </is>
+      </c>
+      <c r="F187" s="6" t="inlineStr">
+        <is>
+          <t>材料物理与化学</t>
+        </is>
+      </c>
+      <c r="G187" s="6" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H187" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I187" s="6" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J187" s="7" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K187" s="7" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L187" s="6" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M187" s="6" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N187" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O187" s="6" t="inlineStr">
+        <is>
+          <t>化学/材料科学</t>
+        </is>
+      </c>
+      <c r="P187" s="6" t="inlineStr"/>
+    </row>
+    <row r="188" ht="16" customHeight="1">
+      <c r="A188" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
+          <t>福州大学</t>
+        </is>
+      </c>
+      <c r="C188" s="4" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="D188" s="4" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E188" s="4" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F188" s="4" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G188" s="4" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H188" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I188" s="4" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J188" s="5" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K188" s="5" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L188" s="4" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M188" s="4" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N188" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O188" s="4" t="inlineStr">
+        <is>
+          <t>化学/材料科学</t>
+        </is>
+      </c>
+      <c r="P188" s="4" t="inlineStr"/>
+    </row>
+    <row r="189" ht="16" customHeight="1">
+      <c r="A189" s="8" t="n">
+        <v>186</v>
+      </c>
+      <c r="B189" s="8" t="inlineStr">
+        <is>
+          <t>福州大学</t>
+        </is>
+      </c>
+      <c r="C189" s="8" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="D189" s="8" t="inlineStr">
+        <is>
+          <t>材料科学与工程学院</t>
+        </is>
+      </c>
+      <c r="E189" s="8" t="inlineStr">
+        <is>
+          <t>085600</t>
+        </is>
+      </c>
+      <c r="F189" s="8" t="inlineStr">
+        <is>
+          <t>材料与化工</t>
+        </is>
+      </c>
+      <c r="G189" s="8" t="inlineStr">
+        <is>
+          <t>专硕</t>
+        </is>
+      </c>
+      <c r="H189" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="I189" s="8" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J189" s="9" t="inlineStr">
+        <is>
+          <t>英语二(204)</t>
+        </is>
+      </c>
+      <c r="K189" s="9" t="inlineStr">
+        <is>
+          <t>数学二(302)</t>
+        </is>
+      </c>
+      <c r="L189" s="8" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="M189" s="8" t="inlineStr">
+        <is>
+          <t>材料科学基础</t>
+        </is>
+      </c>
+      <c r="N189" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O189" s="8" t="inlineStr">
+        <is>
+          <t>化学/材料科学</t>
+        </is>
+      </c>
+      <c r="P189" s="8" t="inlineStr"/>
+    </row>
+    <row r="190" ht="16" customHeight="1">
+      <c r="A190" s="12" t="n">
+        <v>187</v>
+      </c>
+      <c r="B190" s="12" t="inlineStr">
+        <is>
+          <t>中国科学院大学·过程工程研究所</t>
+        </is>
+      </c>
+      <c r="C190" s="12" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="D190" s="12" t="inlineStr">
+        <is>
+          <t>中科院过程工程研究所</t>
+        </is>
+      </c>
+      <c r="E190" s="12" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F190" s="12" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G190" s="12" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H190" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="I190" s="12" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J190" s="13" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K190" s="13" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L190" s="12" t="inlineStr">
+        <is>
+          <t>自命题</t>
+        </is>
+      </c>
+      <c r="M190" s="14" t="inlineStr">
+        <is>
+          <t>材料科学基础*</t>
+        </is>
+      </c>
+      <c r="N190" s="12" t="inlineStr">
+        <is>
+          <t>✓(科研院所)</t>
+        </is>
+      </c>
+      <c r="O190" s="12" t="inlineStr">
+        <is>
+          <t>材料科学/化学工程</t>
+        </is>
+      </c>
+      <c r="P190" s="14" t="inlineStr">
+        <is>
+          <t>高性能陶瓷/功能材料方向，★以UCAS简章为准</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="16" customHeight="1">
+      <c r="A191" s="12" t="n">
+        <v>188</v>
+      </c>
+      <c r="B191" s="12" t="inlineStr">
+        <is>
+          <t>中国科学院大学·化学研究所</t>
+        </is>
+      </c>
+      <c r="C191" s="12" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="D191" s="12" t="inlineStr">
+        <is>
+          <t>中科院化学研究所</t>
+        </is>
+      </c>
+      <c r="E191" s="12" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F191" s="12" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G191" s="12" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H191" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I191" s="12" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J191" s="13" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K191" s="13" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L191" s="12" t="inlineStr">
+        <is>
+          <t>自命题</t>
+        </is>
+      </c>
+      <c r="M191" s="14" t="inlineStr">
+        <is>
+          <t>材料科学基础*</t>
+        </is>
+      </c>
+      <c r="N191" s="12" t="inlineStr">
+        <is>
+          <t>✓(科研院所)</t>
+        </is>
+      </c>
+      <c r="O191" s="12" t="inlineStr">
+        <is>
+          <t>高分子材料/有机功能材料</t>
+        </is>
+      </c>
+      <c r="P191" s="14" t="inlineStr">
+        <is>
+          <t>★以UCAS简章为准</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="16" customHeight="1">
+      <c r="A192" s="12" t="n">
+        <v>189</v>
+      </c>
+      <c r="B192" s="12" t="inlineStr">
+        <is>
+          <t>中国科学院大学·物理研究所</t>
+        </is>
+      </c>
+      <c r="C192" s="12" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="D192" s="12" t="inlineStr">
+        <is>
+          <t>中科院物理研究所</t>
+        </is>
+      </c>
+      <c r="E192" s="12" t="inlineStr">
+        <is>
+          <t>080501</t>
+        </is>
+      </c>
+      <c r="F192" s="12" t="inlineStr">
+        <is>
+          <t>材料物理与化学</t>
+        </is>
+      </c>
+      <c r="G192" s="12" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H192" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="I192" s="12" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J192" s="13" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K192" s="13" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L192" s="12" t="inlineStr">
+        <is>
+          <t>自命题</t>
+        </is>
+      </c>
+      <c r="M192" s="14" t="inlineStr">
+        <is>
+          <t>材料科学基础*</t>
+        </is>
+      </c>
+      <c r="N192" s="12" t="inlineStr">
+        <is>
+          <t>✓(科研院所)</t>
+        </is>
+      </c>
+      <c r="O192" s="12" t="inlineStr">
+        <is>
+          <t>凝聚态物理/材料物理</t>
+        </is>
+      </c>
+      <c r="P192" s="14" t="inlineStr">
+        <is>
+          <t>超导/磁性材料方向，★以UCAS简章为准</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="16" customHeight="1">
+      <c r="A193" s="12" t="n">
+        <v>190</v>
+      </c>
+      <c r="B193" s="12" t="inlineStr">
+        <is>
+          <t>中国科学院大学·大连化物所</t>
+        </is>
+      </c>
+      <c r="C193" s="12" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="D193" s="12" t="inlineStr">
+        <is>
+          <t>中科院大连化学物理研究所</t>
+        </is>
+      </c>
+      <c r="E193" s="12" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F193" s="12" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G193" s="12" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H193" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="I193" s="12" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J193" s="13" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K193" s="13" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L193" s="12" t="inlineStr">
+        <is>
+          <t>自命题</t>
+        </is>
+      </c>
+      <c r="M193" s="14" t="inlineStr">
+        <is>
+          <t>材料科学基础*</t>
+        </is>
+      </c>
+      <c r="N193" s="12" t="inlineStr">
+        <is>
+          <t>✓(科研院所)</t>
+        </is>
+      </c>
+      <c r="O193" s="12" t="inlineStr">
+        <is>
+          <t>能源化学/催化材料</t>
+        </is>
+      </c>
+      <c r="P193" s="14" t="inlineStr">
+        <is>
+          <t>燃料电池/储能材料，★以UCAS简章为准</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="16" customHeight="1">
+      <c r="A194" s="12" t="n">
+        <v>191</v>
+      </c>
+      <c r="B194" s="12" t="inlineStr">
+        <is>
+          <t>中国科学院大学·半导体研究所</t>
+        </is>
+      </c>
+      <c r="C194" s="12" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="D194" s="12" t="inlineStr">
+        <is>
+          <t>中科院半导体研究所</t>
+        </is>
+      </c>
+      <c r="E194" s="12" t="inlineStr">
+        <is>
+          <t>080501</t>
+        </is>
+      </c>
+      <c r="F194" s="12" t="inlineStr">
+        <is>
+          <t>材料物理与化学</t>
+        </is>
+      </c>
+      <c r="G194" s="12" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H194" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="I194" s="12" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J194" s="13" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K194" s="13" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L194" s="12" t="inlineStr">
+        <is>
+          <t>自命题</t>
+        </is>
+      </c>
+      <c r="M194" s="14" t="inlineStr">
+        <is>
+          <t>材料科学基础*</t>
+        </is>
+      </c>
+      <c r="N194" s="12" t="inlineStr">
+        <is>
+          <t>✓(科研院所)</t>
+        </is>
+      </c>
+      <c r="O194" s="12" t="inlineStr">
+        <is>
+          <t>电子科学与技术/材料</t>
+        </is>
+      </c>
+      <c r="P194" s="14" t="inlineStr">
+        <is>
+          <t>半导体/III-V族材料，★以UCAS简章为准</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="16" customHeight="1">
+      <c r="A195" s="12" t="n">
+        <v>192</v>
+      </c>
+      <c r="B195" s="12" t="inlineStr">
+        <is>
+          <t>中国科学院大学·上海光机所</t>
+        </is>
+      </c>
+      <c r="C195" s="12" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="D195" s="12" t="inlineStr">
+        <is>
+          <t>中科院上海光学精密机械研究所</t>
+        </is>
+      </c>
+      <c r="E195" s="12" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F195" s="12" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G195" s="12" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H195" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I195" s="12" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J195" s="13" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K195" s="13" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L195" s="12" t="inlineStr">
+        <is>
+          <t>自命题</t>
+        </is>
+      </c>
+      <c r="M195" s="14" t="inlineStr">
+        <is>
+          <t>材料科学基础*</t>
+        </is>
+      </c>
+      <c r="N195" s="12" t="inlineStr">
+        <is>
+          <t>✓(科研院所)</t>
+        </is>
+      </c>
+      <c r="O195" s="12" t="inlineStr">
+        <is>
+          <t>光学工程/材料</t>
+        </is>
+      </c>
+      <c r="P195" s="14" t="inlineStr">
+        <is>
+          <t>光学玻璃/激光材料，★以UCAS简章为准</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="16" customHeight="1">
+      <c r="A196" s="12" t="n">
+        <v>193</v>
+      </c>
+      <c r="B196" s="12" t="inlineStr">
+        <is>
+          <t>中国科学院大学·理化技术研究所</t>
+        </is>
+      </c>
+      <c r="C196" s="12" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="D196" s="12" t="inlineStr">
+        <is>
+          <t>中科院理化技术研究所</t>
+        </is>
+      </c>
+      <c r="E196" s="12" t="inlineStr">
+        <is>
+          <t>080501</t>
+        </is>
+      </c>
+      <c r="F196" s="12" t="inlineStr">
+        <is>
+          <t>材料物理与化学</t>
+        </is>
+      </c>
+      <c r="G196" s="12" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H196" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I196" s="12" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J196" s="13" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K196" s="13" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L196" s="12" t="inlineStr">
+        <is>
+          <t>自命题</t>
+        </is>
+      </c>
+      <c r="M196" s="14" t="inlineStr">
+        <is>
+          <t>材料科学基础*</t>
+        </is>
+      </c>
+      <c r="N196" s="12" t="inlineStr">
+        <is>
+          <t>✓(科研院所)</t>
+        </is>
+      </c>
+      <c r="O196" s="12" t="inlineStr">
+        <is>
+          <t>材料物理/低温物理</t>
+        </is>
+      </c>
+      <c r="P196" s="14" t="inlineStr">
+        <is>
+          <t>超导/低温材料，★以UCAS简章为准</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="16" customHeight="1">
+      <c r="A197" s="12" t="n">
+        <v>194</v>
+      </c>
+      <c r="B197" s="12" t="inlineStr">
+        <is>
+          <t>中国科学院大学·新疆理化技术研究所</t>
+        </is>
+      </c>
+      <c r="C197" s="12" t="inlineStr">
+        <is>
+          <t>新疆</t>
+        </is>
+      </c>
+      <c r="D197" s="12" t="inlineStr">
+        <is>
+          <t>中科院新疆理化技术研究所</t>
+        </is>
+      </c>
+      <c r="E197" s="12" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F197" s="12" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G197" s="12" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H197" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="I197" s="12" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J197" s="13" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K197" s="13" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L197" s="12" t="inlineStr">
+        <is>
+          <t>自命题</t>
+        </is>
+      </c>
+      <c r="M197" s="14" t="inlineStr">
+        <is>
+          <t>材料科学基础*</t>
+        </is>
+      </c>
+      <c r="N197" s="12" t="inlineStr">
+        <is>
+          <t>✓(科研院所)</t>
+        </is>
+      </c>
+      <c r="O197" s="12" t="inlineStr">
+        <is>
+          <t>材料科学与工程</t>
+        </is>
+      </c>
+      <c r="P197" s="14" t="inlineStr">
+        <is>
+          <t>功能材料/特种材料，★以UCAS简章为准</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="16" customHeight="1">
+      <c r="A198" s="12" t="n">
+        <v>195</v>
+      </c>
+      <c r="B198" s="12" t="inlineStr">
+        <is>
+          <t>中国科学院大学·兰州化学物理所</t>
+        </is>
+      </c>
+      <c r="C198" s="12" t="inlineStr">
+        <is>
+          <t>甘肃</t>
+        </is>
+      </c>
+      <c r="D198" s="12" t="inlineStr">
+        <is>
+          <t>中科院兰州化学物理研究所</t>
+        </is>
+      </c>
+      <c r="E198" s="12" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F198" s="12" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G198" s="12" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H198" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I198" s="12" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J198" s="13" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K198" s="13" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L198" s="12" t="inlineStr">
+        <is>
+          <t>自命题</t>
+        </is>
+      </c>
+      <c r="M198" s="14" t="inlineStr">
+        <is>
+          <t>材料科学基础*</t>
+        </is>
+      </c>
+      <c r="N198" s="12" t="inlineStr">
+        <is>
+          <t>✓(科研院所)</t>
+        </is>
+      </c>
+      <c r="O198" s="12" t="inlineStr">
+        <is>
+          <t>润滑材料/耐磨材料</t>
+        </is>
+      </c>
+      <c r="P198" s="14" t="inlineStr">
+        <is>
+          <t>固体润滑国家重点实验室，★以UCAS简章为准</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="16" customHeight="1">
+      <c r="A199" s="12" t="n">
+        <v>196</v>
+      </c>
+      <c r="B199" s="12" t="inlineStr">
+        <is>
+          <t>中国科学院大学·沈阳自动化研究所</t>
+        </is>
+      </c>
+      <c r="C199" s="12" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="D199" s="12" t="inlineStr">
+        <is>
+          <t>中科院沈阳自动化研究所</t>
+        </is>
+      </c>
+      <c r="E199" s="12" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F199" s="12" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G199" s="12" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H199" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="I199" s="12" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J199" s="13" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K199" s="13" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L199" s="12" t="inlineStr">
+        <is>
+          <t>自命题</t>
+        </is>
+      </c>
+      <c r="M199" s="14" t="inlineStr">
+        <is>
+          <t>材料科学基础*</t>
+        </is>
+      </c>
+      <c r="N199" s="12" t="inlineStr">
+        <is>
+          <t>✓(科研院所)</t>
+        </is>
+      </c>
+      <c r="O199" s="12" t="inlineStr">
+        <is>
+          <t>材料科学与工程</t>
+        </is>
+      </c>
+      <c r="P199" s="14" t="inlineStr">
+        <is>
+          <t>特种材料方向，★以UCAS简章为准</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="16" customHeight="1">
+      <c r="A200" s="12" t="n">
+        <v>197</v>
+      </c>
+      <c r="B200" s="12" t="inlineStr">
+        <is>
+          <t>中国科学院大学·广州能源研究所</t>
+        </is>
+      </c>
+      <c r="C200" s="12" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="D200" s="12" t="inlineStr">
+        <is>
+          <t>中科院广州能源研究所</t>
+        </is>
+      </c>
+      <c r="E200" s="12" t="inlineStr">
+        <is>
+          <t>080502</t>
+        </is>
+      </c>
+      <c r="F200" s="12" t="inlineStr">
+        <is>
+          <t>材料学</t>
+        </is>
+      </c>
+      <c r="G200" s="12" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H200" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I200" s="12" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J200" s="13" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K200" s="13" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L200" s="12" t="inlineStr">
+        <is>
+          <t>自命题</t>
+        </is>
+      </c>
+      <c r="M200" s="14" t="inlineStr">
+        <is>
+          <t>材料科学基础*</t>
+        </is>
+      </c>
+      <c r="N200" s="12" t="inlineStr">
+        <is>
+          <t>✓(科研院所)</t>
+        </is>
+      </c>
+      <c r="O200" s="12" t="inlineStr">
+        <is>
+          <t>能源/材料科学</t>
+        </is>
+      </c>
+      <c r="P200" s="14" t="inlineStr">
+        <is>
+          <t>储能材料方向，★以UCAS简章为准</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="16" customHeight="1">
+      <c r="A201" s="12" t="n">
+        <v>198</v>
+      </c>
+      <c r="B201" s="12" t="inlineStr">
+        <is>
+          <t>中国科学院大学·金属腐蚀与防护国家重点实验室</t>
+        </is>
+      </c>
+      <c r="C201" s="12" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="D201" s="12" t="inlineStr">
+        <is>
+          <t>中科院金属研究所（腐蚀防护）</t>
+        </is>
+      </c>
+      <c r="E201" s="12" t="inlineStr">
+        <is>
+          <t>080501</t>
+        </is>
+      </c>
+      <c r="F201" s="12" t="inlineStr">
+        <is>
+          <t>材料物理与化学</t>
+        </is>
+      </c>
+      <c r="G201" s="12" t="inlineStr">
+        <is>
+          <t>学硕</t>
+        </is>
+      </c>
+      <c r="H201" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="I201" s="12" t="inlineStr">
+        <is>
+          <t>思政(101)</t>
+        </is>
+      </c>
+      <c r="J201" s="13" t="inlineStr">
+        <is>
+          <t>英语一(201)</t>
+        </is>
+      </c>
+      <c r="K201" s="13" t="inlineStr">
+        <is>
+          <t>数学一(301)</t>
+        </is>
+      </c>
+      <c r="L201" s="12" t="inlineStr">
+        <is>
+          <t>自命题</t>
+        </is>
+      </c>
+      <c r="M201" s="14" t="inlineStr">
+        <is>
+          <t>材料科学基础*</t>
+        </is>
+      </c>
+      <c r="N201" s="12" t="inlineStr">
+        <is>
+          <t>✓(科研院所)</t>
+        </is>
+      </c>
+      <c r="O201" s="12" t="inlineStr">
+        <is>
+          <t>材料科学与工程</t>
+        </is>
+      </c>
+      <c r="P201" s="14" t="inlineStr">
+        <is>
+          <t>腐蚀防护国重，★以UCAS简章为准</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:P86"/>
+  <autoFilter ref="A2:P201"/>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A3:P3"/>
